--- a/admin/additional_payment.xlsx
+++ b/admin/additional_payment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E5AA3C-8F30-4AE2-BF11-7EE794D02E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46BE2754-691D-4A2E-94D3-C7029704FDAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{15A88CCE-3372-449C-83CE-515127A63710}"/>
   </bookViews>
@@ -75,28 +75,28 @@
     <t>December</t>
   </si>
   <si>
-    <t>00001</t>
-  </si>
-  <si>
-    <t>00002</t>
-  </si>
-  <si>
-    <t>00003</t>
-  </si>
-  <si>
-    <t>00004</t>
-  </si>
-  <si>
-    <t>00005</t>
-  </si>
-  <si>
-    <t>00006</t>
-  </si>
-  <si>
-    <t>00007</t>
-  </si>
-  <si>
-    <t>Additional Payment</t>
+    <t>Arear</t>
+  </si>
+  <si>
+    <t>Other Reimbursement</t>
+  </si>
+  <si>
+    <t>Increment Arear</t>
+  </si>
+  <si>
+    <t>Bonus</t>
+  </si>
+  <si>
+    <t>Leave encasement</t>
+  </si>
+  <si>
+    <t>Notice period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	1001</t>
+  </si>
+  <si>
+    <t>3780</t>
   </si>
 </sst>
 </file>
@@ -494,6 +494,10 @@
   <cols>
     <col min="1" max="1" width="15.140625" style="5" customWidth="1"/>
     <col min="2" max="2" width="18.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -502,70 +506,80 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" t="s">
+        <v>18</v>
       </c>
       <c r="AC1" s="1"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B2" s="3">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>12</v>
+      </c>
+      <c r="D2">
+        <v>13</v>
+      </c>
+      <c r="E2">
+        <v>13</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>10</v>
       </c>
       <c r="AC2" s="1"/>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B3" s="3">
-        <v>4</v>
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>13</v>
+      </c>
+      <c r="D3">
+        <v>13</v>
+      </c>
+      <c r="E3">
+        <v>13</v>
+      </c>
+      <c r="F3">
+        <v>13</v>
       </c>
       <c r="AC3" s="1"/>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="3">
-        <v>6</v>
-      </c>
       <c r="AC4" s="1"/>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="3">
-        <v>8</v>
-      </c>
-    </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="3">
-        <v>10</v>
-      </c>
       <c r="AC6" s="1"/>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="3">
-        <v>12</v>
-      </c>
       <c r="AC7" s="1"/>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="3">
-        <v>14</v>
-      </c>
       <c r="AC8" s="1"/>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.25">
